--- a/astro-site/public/dl/kit-inventario/01-inventario-stock-diario.xlsx
+++ b/astro-site/public/dl/kit-inventario/01-inventario-stock-diario.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cocina" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Barra" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Almacén" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Resumen Dashboard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocina" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barra" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Almacén" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Dashboard" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cocina'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Barra'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Almacén'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -106,34 +110,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -493,12 +497,12 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="80"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,8 +633,25 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-inventario · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -639,23 +660,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="8"/>
-    <col customWidth="1" max="5" min="5" width="10"/>
-    <col customWidth="1" max="6" min="6" width="10"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="10"/>
-    <col customWidth="1" max="9" min="9" width="10"/>
-    <col customWidth="1" max="10" min="10" width="10"/>
-    <col customWidth="1" max="11" min="11" width="18"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -672,6 +693,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1494,6 +1516,8 @@
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
@@ -1507,7 +1531,16 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1516,23 +1549,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="8"/>
-    <col customWidth="1" max="5" min="5" width="10"/>
-    <col customWidth="1" max="6" min="6" width="10"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="10"/>
-    <col customWidth="1" max="9" min="9" width="10"/>
-    <col customWidth="1" max="10" min="10" width="10"/>
-    <col customWidth="1" max="11" min="11" width="18"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1549,6 +1582,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -2181,6 +2215,8 @@
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -2194,7 +2230,16 @@
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2203,23 +2248,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="8"/>
-    <col customWidth="1" max="5" min="5" width="10"/>
-    <col customWidth="1" max="6" min="6" width="10"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="10"/>
-    <col customWidth="1" max="9" min="9" width="10"/>
-    <col customWidth="1" max="10" min="10" width="10"/>
-    <col customWidth="1" max="11" min="11" width="18"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2236,6 +2281,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -2868,6 +2914,8 @@
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -2881,7 +2929,16 @@
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2890,15 +2947,15 @@
   <sheetPr>
     <tabColor rgb="0000C853"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="20"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="20"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2908,6 +2965,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2930,7 +2988,17 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-inventario/01-inventario-stock-diario.xlsx
+++ b/astro-site/public/dl/kit-inventario/01-inventario-stock-diario.xlsx
@@ -15,8 +15,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cocina'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Cocina'!$A$1:$M$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Barra'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Barra'!$A$1:$M$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Almacén'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Almacén'!$A$1:$M$37</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Resumen Dashboard'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Resumen Dashboard'!$A$1:$D$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,8 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,8 +75,16 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +99,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,10 +154,74 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -499,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -520,24 +605,24 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Este archivo te permite controlar el stock diario de tu restaurante.</t>
+          <t>Controla el stock diario de tu restaurante: qué tienes, qué te falta y cuánto vale.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Cada pestaña corresponde a una zona: Cocina, Barra, Almacén.</t>
+          <t>Cada pestaña es una zona de conteo (Cocina, Barra y Almacén) y la pestaña Resumen Dashboard las totaliza.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
+      <c r="A6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -549,95 +634,144 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>1. Rellena la columna 'Producto' con tus ingredientes.</t>
+          <t>1. Revisa los productos de ejemplo y sustitúyelos por los tuyos. Las columnas Categoría y Unidad tienen desplegable: úsalo, porque los análisis del kit agregan por ese texto.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2. Establece 'Par Level' (stock mínimo) y 'Par Max' (stock máximo).</t>
+          <t>2. Ajusta Par Level (stock mínimo de trabajo) y Par Max (hasta dónde repones) producto a producto.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3. Cada día, anota el stock actual en 'Stock Real'.</t>
+          <t>3. Escribe el precio de compra SIN IVA en Precio/ud (€): es lo que hace que la columna Valor (€) y el resumen funcionen.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>4. La columna 'Estado' se colorea automáticamente:</t>
+          <t>4. Cada día anota lo que cuentas en Stock Real.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   🔴 Rojo = por debajo del par level → ¡pedir!</t>
+          <t>5. La columna Estado se colorea sola:</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   🟡 Amarillo = stock bajo, vigilar</t>
+          <t xml:space="preserve">   🔴 PEDIR = por debajo del par level</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   🟢 Verde = stock correcto</t>
+          <t xml:space="preserve">   🟡 BAJO = entre el par level y una vez y media el par level</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>5. 'A Pedir' calcula automáticamente cuánto necesitas.</t>
+          <t xml:space="preserve">   🟢 OK = por encima</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>6. A Pedir calcula cuánto reponer hasta el Par Max ya en ámbar, no sólo en rojo: si esperas al rojo, con dos días de plazo de entrega llegas tarde.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>PERSONALIZACIÓN:</t>
+          <t>7. Estado y A Pedir se quedan EN BLANCO mientras la fila no tenga par level: en las filas libres del final no hay ninguno, y decirte «OK» comparando contra una casilla vacía sería mentirte justo en el producto que acabas de dar de alta.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>- Añade o elimina filas según tus productos.</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>- Ajusta los par levels a tu ritmo de ventas.</t>
+          <t>PERSONALIZACIÓN:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>- La pestaña 'Resumen' totaliza automáticamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+          <t>- Hay filas libres al final de cada zona: Cocina hasta la 44, Barra y Almacén hasta la 34.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>- EL PAR LEVEL ES TU PUNTO DE PEDIDO. Sale de: consumo diario × (plazo de entrega + días de cobertura de seguridad). Es exactamente la misma cuenta que hace el BONUS-09, así que los dos ficheros dan el mismo número para el mismo producto: no hay dos reglas, hay una.</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-inventario · info@aichef.pro</t>
+          <t>- Y el Par Max es el techo: la cantidad sugerida del BONUS-09 nunca lo supera, porque de nada sirve que la fórmula mande pedir más de lo que te cabe en cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>- Una misma referencia puede aparecer en DOS zonas (las servilletas están en Barra y en Almacén): es stock por ubicación y cada zona lleva su propio par level. El resumen las cuenta por separado a propósito; el pedido se consolida en la plantilla 03, que es donde cuentan el pedido mínimo, los portes y el rappel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>- La pestaña Resumen Dashboard totaliza el stock bajo, los productos a pedir y el valor del stock por zona y por categoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>- Los 50 productos, con sus categorías, unidades, par levels y precios, son un ejemplo real de restaurante: revísalos con tus datos antes de usarlos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Para editar una celda bloqueada: Revisar → Desproteger hoja (no tiene contraseña). Las celdas verdes ya son editables sin desproteger nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-inventario · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -662,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -674,9 +808,10 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -693,7 +828,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Datos de ejemplo; precios orientativos SIN IVA, edítalos con los tuyos. Categoría y Unidad tienen desplegable.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -742,15 +883,20 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
+          <t>Precio/ud (€)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
           <t>Valor (€)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -760,777 +906,1437 @@
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Pechuga de pollo</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Cárnicos</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr"/>
       <c r="H5" s="8">
-        <f>IF(G5="","",IF(G5&lt;E5,"🔴 PEDIR",IF(G5&lt;E5*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G5="",$E5=""),"",IF($G5&lt;$E5,"🔴 PEDIR",IF($G5&lt;$E5*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>IF(G5="","",IF(G5&lt;E5,F5-G5,0))</f>
-        <v/>
-      </c>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
+        <f>IF(OR($G5="",$E5="",$F5=""),"",IF($G5&lt;$E5*1.5,MAX(0,$F5-$G5),0))</f>
+        <v/>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K5" s="16">
+        <f>IFERROR(IF(OR($G5="",$J5=""),"",$G5*$J5),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Solomillo ternera</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Lácteos</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Solomillo de ternera</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Cárnicos</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr"/>
       <c r="H6" s="9">
-        <f>IF(G6="","",IF(G6&lt;E6,"🔴 PEDIR",IF(G6&lt;E6*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G6="",$E6=""),"",IF($G6&lt;$E6,"🔴 PEDIR",IF($G6&lt;$E6*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>IF(G6="","",IF(G6&lt;E6,F6-G6,0))</f>
-        <v/>
-      </c>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
+        <f>IF(OR($G6="",$E6="",$F6=""),"",IF($G6&lt;$E6*1.5,MAX(0,$F6-$G6),0))</f>
+        <v/>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" s="17">
+        <f>IFERROR(IF(OR($G6="",$J6=""),"",$G6*$J6),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Salmón fresco</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Verduras</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Pescados</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
+      <c r="E7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr"/>
       <c r="H7" s="8">
-        <f>IF(G7="","",IF(G7&lt;E7,"🔴 PEDIR",IF(G7&lt;E7*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G7="",$E7=""),"",IF($G7&lt;$E7,"🔴 PEDIR",IF($G7&lt;$E7*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IF(G7="","",IF(G7&lt;E7,F7-G7,0))</f>
-        <v/>
-      </c>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
+        <f>IF(OR($G7="",$E7="",$F7=""),"",IF($G7&lt;$E7*1.5,MAX(0,$F7-$G7),0))</f>
+        <v/>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" s="16">
+        <f>IFERROR(IF(OR($G7="",$J7=""),"",$G7*$J7),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Gambas</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Frutas</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Pescados</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr"/>
       <c r="H8" s="9">
-        <f>IF(G8="","",IF(G8&lt;E8,"🔴 PEDIR",IF(G8&lt;E8*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G8="",$E8=""),"",IF($G8&lt;$E8,"🔴 PEDIR",IF($G8&lt;$E8*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IF(G8="","",IF(G8&lt;E8,F8-G8,0))</f>
-        <v/>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
+        <f>IF(OR($G8="",$E8="",$F8=""),"",IF($G8&lt;$E8*1.5,MAX(0,$F8-$G8),0))</f>
+        <v/>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" s="17">
+        <f>IFERROR(IF(OR($G8="",$J8=""),"",$G8*$J8),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Secos/Granos</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Verduras/Frutas</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr"/>
       <c r="H9" s="8">
-        <f>IF(G9="","",IF(G9&lt;E9,"🔴 PEDIR",IF(G9&lt;E9*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G9="",$E9=""),"",IF($G9&lt;$E9,"🔴 PEDIR",IF($G9&lt;$E9*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>IF(G9="","",IF(G9&lt;E9,F9-G9,0))</f>
-        <v/>
-      </c>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
+        <f>IF(OR($G9="",$E9="",$F9=""),"",IF($G9&lt;$E9*1.5,MAX(0,$F9-$G9),0))</f>
+        <v/>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K9" s="16">
+        <f>IFERROR(IF(OR($G9="",$J9=""),"",$G9*$J9),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Cebolla</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Congelados</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Verduras/Frutas</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
+      <c r="E10" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="14" t="inlineStr"/>
       <c r="H10" s="9">
-        <f>IF(G10="","",IF(G10&lt;E10,"🔴 PEDIR",IF(G10&lt;E10*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G10="",$E10=""),"",IF($G10&lt;$E10,"🔴 PEDIR",IF($G10&lt;$E10*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IF(G10="","",IF(G10&lt;E10,F10-G10,0))</f>
-        <v/>
-      </c>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
+        <f>IF(OR($G10="",$E10="",$F10=""),"",IF($G10&lt;$E10*1.5,MAX(0,$F10-$G10),0))</f>
+        <v/>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K10" s="17">
+        <f>IFERROR(IF(OR($G10="",$J10=""),"",$G10*$J10),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Lechuga</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Verduras/Frutas</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="E11" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr"/>
       <c r="H11" s="8">
-        <f>IF(G11="","",IF(G11&lt;E11,"🔴 PEDIR",IF(G11&lt;E11*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G11="",$E11=""),"",IF($G11&lt;$E11,"🔴 PEDIR",IF($G11&lt;$E11*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I11" s="8">
-        <f>IF(G11="","",IF(G11&lt;E11,F11-G11,0))</f>
-        <v/>
-      </c>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
+        <f>IF(OR($G11="",$E11="",$F11=""),"",IF($G11&lt;$E11*1.5,MAX(0,$F11-$G11),0))</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K11" s="16">
+        <f>IFERROR(IF(OR($G11="",$J11=""),"",$G11*$J11),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Patata</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Verduras/Frutas</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr"/>
       <c r="H12" s="9">
-        <f>IF(G12="","",IF(G12&lt;E12,"🔴 PEDIR",IF(G12&lt;E12*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G12="",$E12=""),"",IF($G12&lt;$E12,"🔴 PEDIR",IF($G12&lt;$E12*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IF(G12="","",IF(G12&lt;E12,F12-G12,0))</f>
-        <v/>
-      </c>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
+        <f>IF(OR($G12="",$E12="",$F12=""),"",IF($G12&lt;$E12*1.5,MAX(0,$F12-$G12),0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K12" s="17">
+        <f>IFERROR(IF(OR($G12="",$J12=""),"",$G12*$J12),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Aceite oliva</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Varios</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Aceite de oliva virgen extra</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr"/>
       <c r="H13" s="8">
-        <f>IF(G13="","",IF(G13&lt;E13,"🔴 PEDIR",IF(G13&lt;E13*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G13="",$E13=""),"",IF($G13&lt;$E13,"🔴 PEDIR",IF($G13&lt;$E13*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I13" s="8">
-        <f>IF(G13="","",IF(G13&lt;E13,F13-G13,0))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
+        <f>IF(OR($G13="",$E13="",$F13=""),"",IF($G13&lt;$E13*1.5,MAX(0,$F13-$G13),0))</f>
+        <v/>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K13" s="16">
+        <f>IFERROR(IF(OR($G13="",$J13=""),"",$G13*$J13),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Sal</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cárnicos</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr"/>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Sal marina</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr"/>
       <c r="H14" s="9">
-        <f>IF(G14="","",IF(G14&lt;E14,"🔴 PEDIR",IF(G14&lt;E14*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G14="",$E14=""),"",IF($G14&lt;$E14,"🔴 PEDIR",IF($G14&lt;$E14*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I14" s="9">
-        <f>IF(G14="","",IF(G14&lt;E14,F14-G14,0))</f>
-        <v/>
-      </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
+        <f>IF(OR($G14="",$E14="",$F14=""),"",IF($G14&lt;$E14*1.5,MAX(0,$F14-$G14),0))</f>
+        <v/>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K14" s="17">
+        <f>IFERROR(IF(OR($G14="",$J14=""),"",$G14*$J14),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Pimienta</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Pimienta negra molida</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="8">
-        <f>IF(G15="","",IF(G15&lt;E15,"🔴 PEDIR",IF(G15&lt;E15*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G15="",$E15=""),"",IF($G15&lt;$E15,"🔴 PEDIR",IF($G15&lt;$E15*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IF(G15="","",IF(G15&lt;E15,F15-G15,0))</f>
-        <v/>
-      </c>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
+        <f>IF(OR($G15="",$E15="",$F15=""),"",IF($G15&lt;$E15*1.5,MAX(0,$F15-$G15),0))</f>
+        <v/>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="16">
+        <f>IFERROR(IF(OR($G15="",$J15=""),"",$G15*$J15),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Arroz</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Lácteos</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Arroz redondo</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr"/>
+      <c r="E16" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr"/>
       <c r="H16" s="9">
-        <f>IF(G16="","",IF(G16&lt;E16,"🔴 PEDIR",IF(G16&lt;E16*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G16="",$E16=""),"",IF($G16&lt;$E16,"🔴 PEDIR",IF($G16&lt;$E16*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I16" s="9">
-        <f>IF(G16="","",IF(G16&lt;E16,F16-G16,0))</f>
-        <v/>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
+        <f>IF(OR($G16="",$E16="",$F16=""),"",IF($G16&lt;$E16*1.5,MAX(0,$F16-$G16),0))</f>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K16" s="17">
+        <f>IFERROR(IF(OR($G16="",$J16=""),"",$G16*$J16),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Pasta seca</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Verduras</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="8">
-        <f>IF(G17="","",IF(G17&lt;E17,"🔴 PEDIR",IF(G17&lt;E17*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G17="",$E17=""),"",IF($G17&lt;$E17,"🔴 PEDIR",IF($G17&lt;$E17*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I17" s="8">
-        <f>IF(G17="","",IF(G17&lt;E17,F17-G17,0))</f>
-        <v/>
-      </c>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
+        <f>IF(OR($G17="",$E17="",$F17=""),"",IF($G17&lt;$E17*1.5,MAX(0,$F17-$G17),0))</f>
+        <v/>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K17" s="16">
+        <f>IFERROR(IF(OR($G17="",$J17=""),"",$G17*$J17),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Harina</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Frutas</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr"/>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr"/>
       <c r="H18" s="9">
-        <f>IF(G18="","",IF(G18&lt;E18,"🔴 PEDIR",IF(G18&lt;E18*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G18="",$E18=""),"",IF($G18&lt;$E18,"🔴 PEDIR",IF($G18&lt;$E18*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I18" s="9">
-        <f>IF(G18="","",IF(G18&lt;E18,F18-G18,0))</f>
-        <v/>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
+        <f>IF(OR($G18="",$E18="",$F18=""),"",IF($G18&lt;$E18*1.5,MAX(0,$F18-$G18),0))</f>
+        <v/>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K18" s="17">
+        <f>IFERROR(IF(OR($G18="",$J18=""),"",$G18*$J18),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Huevos</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Secos/Granos</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="8" t="n">
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Huevos M</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>docena</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="F19" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr"/>
       <c r="H19" s="8">
-        <f>IF(G19="","",IF(G19&lt;E19,"🔴 PEDIR",IF(G19&lt;E19*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G19="",$E19=""),"",IF($G19&lt;$E19,"🔴 PEDIR",IF($G19&lt;$E19*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I19" s="8">
-        <f>IF(G19="","",IF(G19&lt;E19,F19-G19,0))</f>
-        <v/>
-      </c>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
+        <f>IF(OR($G19="",$E19="",$F19=""),"",IF($G19&lt;$E19*1.5,MAX(0,$F19-$G19),0))</f>
+        <v/>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K19" s="16">
+        <f>IFERROR(IF(OR($G19="",$J19=""),"",$G19*$J19),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Nata</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Congelados</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" s="9" t="n">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Nata 35 % M.G.</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G20" s="9" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr"/>
       <c r="H20" s="9">
-        <f>IF(G20="","",IF(G20&lt;E20,"🔴 PEDIR",IF(G20&lt;E20*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G20="",$E20=""),"",IF($G20&lt;$E20,"🔴 PEDIR",IF($G20&lt;$E20*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I20" s="9">
-        <f>IF(G20="","",IF(G20&lt;E20,F20-G20,0))</f>
-        <v/>
-      </c>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
+        <f>IF(OR($G20="",$E20="",$F20=""),"",IF($G20&lt;$E20*1.5,MAX(0,$F20-$G20),0))</f>
+        <v/>
+      </c>
+      <c r="J20" s="15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K20" s="17">
+        <f>IFERROR(IF(OR($G20="",$J20=""),"",$G20*$J20),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Mantequilla</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" s="8" t="inlineStr"/>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr"/>
       <c r="H21" s="8">
-        <f>IF(G21="","",IF(G21&lt;E21,"🔴 PEDIR",IF(G21&lt;E21*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G21="",$E21=""),"",IF($G21&lt;$E21,"🔴 PEDIR",IF($G21&lt;$E21*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I21" s="8">
-        <f>IF(G21="","",IF(G21&lt;E21,F21-G21,0))</f>
-        <v/>
-      </c>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
+        <f>IF(OR($G21="",$E21="",$F21=""),"",IF($G21&lt;$E21*1.5,MAX(0,$F21-$G21),0))</f>
+        <v/>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K21" s="16">
+        <f>IFERROR(IF(OR($G21="",$J21=""),"",$G21*$J21),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Queso parmesano</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" s="9" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr"/>
       <c r="H22" s="9">
-        <f>IF(G22="","",IF(G22&lt;E22,"🔴 PEDIR",IF(G22&lt;E22*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G22="",$E22=""),"",IF($G22&lt;$E22,"🔴 PEDIR",IF($G22&lt;$E22*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I22" s="9">
-        <f>IF(G22="","",IF(G22&lt;E22,F22-G22,0))</f>
-        <v/>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
+        <f>IF(OR($G22="",$E22="",$F22=""),"",IF($G22&lt;$E22*1.5,MAX(0,$F22-$G22),0))</f>
+        <v/>
+      </c>
+      <c r="J22" s="15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K22" s="17">
+        <f>IFERROR(IF(OR($G22="",$J22=""),"",$G22*$J22),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Limón</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Varios</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="n">
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Verduras/Frutas</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G23" s="8" t="inlineStr"/>
+      <c r="F23" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr"/>
       <c r="H23" s="8">
-        <f>IF(G23="","",IF(G23&lt;E23,"🔴 PEDIR",IF(G23&lt;E23*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G23="",$E23=""),"",IF($G23&lt;$E23,"🔴 PEDIR",IF($G23&lt;$E23*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I23" s="8">
-        <f>IF(G23="","",IF(G23&lt;E23,F23-G23,0))</f>
-        <v/>
-      </c>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
+        <f>IF(OR($G23="",$E23="",$F23=""),"",IF($G23&lt;$E23*1.5,MAX(0,$F23-$G23),0))</f>
+        <v/>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K23" s="16">
+        <f>IFERROR(IF(OR($G23="",$J23=""),"",$G23*$J23),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Ajo</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Cárnicos</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr"/>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Verduras/Frutas</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="14" t="inlineStr"/>
       <c r="H24" s="9">
-        <f>IF(G24="","",IF(G24&lt;E24,"🔴 PEDIR",IF(G24&lt;E24*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G24="",$E24=""),"",IF($G24&lt;$E24,"🔴 PEDIR",IF($G24&lt;$E24*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I24" s="9">
-        <f>IF(G24="","",IF(G24&lt;E24,F24-G24,0))</f>
-        <v/>
-      </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+        <f>IF(OR($G24="",$E24="",$F24=""),"",IF($G24&lt;$E24*1.5,MAX(0,$F24-$G24),0))</f>
+        <v/>
+      </c>
+      <c r="J24" s="15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K24" s="17">
+        <f>IFERROR(IF(OR($G24="",$J24=""),"",$G24*$J24),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="8">
+        <f>IF(OR($G25="",$E25=""),"",IF($G25&lt;$E25,"🔴 PEDIR",IF($G25&lt;$E25*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I25" s="8">
+        <f>IF(OR($G25="",$E25="",$F25=""),"",IF($G25&lt;$E25*1.5,MAX(0,$F25-$G25),0))</f>
+        <v/>
+      </c>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="16">
+        <f>IFERROR(IF(OR($G25="",$J25=""),"",$G25*$J25),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="9">
+        <f>IF(OR($G26="",$E26=""),"",IF($G26&lt;$E26,"🔴 PEDIR",IF($G26&lt;$E26*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>IF(OR($G26="",$E26="",$F26=""),"",IF($G26&lt;$E26*1.5,MAX(0,$F26-$G26),0))</f>
+        <v/>
+      </c>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="17">
+        <f>IFERROR(IF(OR($G26="",$J26=""),"",$G26*$J26),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="8">
+        <f>IF(OR($G27="",$E27=""),"",IF($G27&lt;$E27,"🔴 PEDIR",IF($G27&lt;$E27*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I27" s="8">
+        <f>IF(OR($G27="",$E27="",$F27=""),"",IF($G27&lt;$E27*1.5,MAX(0,$F27-$G27),0))</f>
+        <v/>
+      </c>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="16">
+        <f>IFERROR(IF(OR($G27="",$J27=""),"",$G27*$J27),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="9">
+        <f>IF(OR($G28="",$E28=""),"",IF($G28&lt;$E28,"🔴 PEDIR",IF($G28&lt;$E28*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>IF(OR($G28="",$E28="",$F28=""),"",IF($G28&lt;$E28*1.5,MAX(0,$F28-$G28),0))</f>
+        <v/>
+      </c>
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="17">
+        <f>IFERROR(IF(OR($G28="",$J28=""),"",$G28*$J28),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="8">
+        <f>IF(OR($G29="",$E29=""),"",IF($G29&lt;$E29,"🔴 PEDIR",IF($G29&lt;$E29*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I29" s="8">
+        <f>IF(OR($G29="",$E29="",$F29=""),"",IF($G29&lt;$E29*1.5,MAX(0,$F29-$G29),0))</f>
+        <v/>
+      </c>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="16">
+        <f>IFERROR(IF(OR($G29="",$J29=""),"",$G29*$J29),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="9">
+        <f>IF(OR($G30="",$E30=""),"",IF($G30&lt;$E30,"🔴 PEDIR",IF($G30&lt;$E30*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>IF(OR($G30="",$E30="",$F30=""),"",IF($G30&lt;$E30*1.5,MAX(0,$F30-$G30),0))</f>
+        <v/>
+      </c>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="17">
+        <f>IFERROR(IF(OR($G30="",$J30=""),"",$G30*$J30),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="8">
+        <f>IF(OR($G31="",$E31=""),"",IF($G31&lt;$E31,"🔴 PEDIR",IF($G31&lt;$E31*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I31" s="8">
+        <f>IF(OR($G31="",$E31="",$F31=""),"",IF($G31&lt;$E31*1.5,MAX(0,$F31-$G31),0))</f>
+        <v/>
+      </c>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="16">
+        <f>IFERROR(IF(OR($G31="",$J31=""),"",$G31*$J31),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="9">
+        <f>IF(OR($G32="",$E32=""),"",IF($G32&lt;$E32,"🔴 PEDIR",IF($G32&lt;$E32*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I32" s="9">
+        <f>IF(OR($G32="",$E32="",$F32=""),"",IF($G32&lt;$E32*1.5,MAX(0,$F32-$G32),0))</f>
+        <v/>
+      </c>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="17">
+        <f>IFERROR(IF(OR($G32="",$J32=""),"",$G32*$J32),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="8">
+        <f>IF(OR($G33="",$E33=""),"",IF($G33&lt;$E33,"🔴 PEDIR",IF($G33&lt;$E33*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>IF(OR($G33="",$E33="",$F33=""),"",IF($G33&lt;$E33*1.5,MAX(0,$F33-$G33),0))</f>
+        <v/>
+      </c>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="16">
+        <f>IFERROR(IF(OR($G33="",$J33=""),"",$G33*$J33),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="9">
+        <f>IF(OR($G34="",$E34=""),"",IF($G34&lt;$E34,"🔴 PEDIR",IF($G34&lt;$E34*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I34" s="9">
+        <f>IF(OR($G34="",$E34="",$F34=""),"",IF($G34&lt;$E34*1.5,MAX(0,$F34-$G34),0))</f>
+        <v/>
+      </c>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="17">
+        <f>IFERROR(IF(OR($G34="",$J34=""),"",$G34*$J34),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="8">
+        <f>IF(OR($G35="",$E35=""),"",IF($G35&lt;$E35,"🔴 PEDIR",IF($G35&lt;$E35*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I35" s="8">
+        <f>IF(OR($G35="",$E35="",$F35=""),"",IF($G35&lt;$E35*1.5,MAX(0,$F35-$G35),0))</f>
+        <v/>
+      </c>
+      <c r="J35" s="15" t="n"/>
+      <c r="K35" s="16">
+        <f>IFERROR(IF(OR($G35="",$J35=""),"",$G35*$J35),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="9">
+        <f>IF(OR($G36="",$E36=""),"",IF($G36&lt;$E36,"🔴 PEDIR",IF($G36&lt;$E36*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I36" s="9">
+        <f>IF(OR($G36="",$E36="",$F36=""),"",IF($G36&lt;$E36*1.5,MAX(0,$F36-$G36),0))</f>
+        <v/>
+      </c>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="17">
+        <f>IFERROR(IF(OR($G36="",$J36=""),"",$G36*$J36),"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="8">
+        <f>IF(OR($G37="",$E37=""),"",IF($G37&lt;$E37,"🔴 PEDIR",IF($G37&lt;$E37*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I37" s="8">
+        <f>IF(OR($G37="",$E37="",$F37=""),"",IF($G37&lt;$E37*1.5,MAX(0,$F37-$G37),0))</f>
+        <v/>
+      </c>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="16">
+        <f>IFERROR(IF(OR($G37="",$J37=""),"",$G37*$J37),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="9">
+        <f>IF(OR($G38="",$E38=""),"",IF($G38&lt;$E38,"🔴 PEDIR",IF($G38&lt;$E38*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I38" s="9">
+        <f>IF(OR($G38="",$E38="",$F38=""),"",IF($G38&lt;$E38*1.5,MAX(0,$F38-$G38),0))</f>
+        <v/>
+      </c>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="17">
+        <f>IFERROR(IF(OR($G38="",$J38=""),"",$G38*$J38),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="8">
+        <f>IF(OR($G39="",$E39=""),"",IF($G39&lt;$E39,"🔴 PEDIR",IF($G39&lt;$E39*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I39" s="8">
+        <f>IF(OR($G39="",$E39="",$F39=""),"",IF($G39&lt;$E39*1.5,MAX(0,$F39-$G39),0))</f>
+        <v/>
+      </c>
+      <c r="J39" s="15" t="n"/>
+      <c r="K39" s="16">
+        <f>IFERROR(IF(OR($G39="",$J39=""),"",$G39*$J39),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="9">
+        <f>IF(OR($G40="",$E40=""),"",IF($G40&lt;$E40,"🔴 PEDIR",IF($G40&lt;$E40*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I40" s="9">
+        <f>IF(OR($G40="",$E40="",$F40=""),"",IF($G40&lt;$E40*1.5,MAX(0,$F40-$G40),0))</f>
+        <v/>
+      </c>
+      <c r="J40" s="15" t="n"/>
+      <c r="K40" s="17">
+        <f>IFERROR(IF(OR($G40="",$J40=""),"",$G40*$J40),"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="8">
+        <f>IF(OR($G41="",$E41=""),"",IF($G41&lt;$E41,"🔴 PEDIR",IF($G41&lt;$E41*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I41" s="8">
+        <f>IF(OR($G41="",$E41="",$F41=""),"",IF($G41&lt;$E41*1.5,MAX(0,$F41-$G41),0))</f>
+        <v/>
+      </c>
+      <c r="J41" s="15" t="n"/>
+      <c r="K41" s="16">
+        <f>IFERROR(IF(OR($G41="",$J41=""),"",$G41*$J41),"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="9">
+        <f>IF(OR($G42="",$E42=""),"",IF($G42&lt;$E42,"🔴 PEDIR",IF($G42&lt;$E42*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I42" s="9">
+        <f>IF(OR($G42="",$E42="",$F42=""),"",IF($G42&lt;$E42*1.5,MAX(0,$F42-$G42),0))</f>
+        <v/>
+      </c>
+      <c r="J42" s="15" t="n"/>
+      <c r="K42" s="17">
+        <f>IFERROR(IF(OR($G42="",$J42=""),"",$G42*$J42),"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="14" t="n"/>
+      <c r="H43" s="8">
+        <f>IF(OR($G43="",$E43=""),"",IF($G43&lt;$E43,"🔴 PEDIR",IF($G43&lt;$E43*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I43" s="8">
+        <f>IF(OR($G43="",$E43="",$F43=""),"",IF($G43&lt;$E43*1.5,MAX(0,$F43-$G43),0))</f>
+        <v/>
+      </c>
+      <c r="J43" s="15" t="n"/>
+      <c r="K43" s="16">
+        <f>IFERROR(IF(OR($G43="",$J43=""),"",$G43*$J43),"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="9">
+        <f>IF(OR($G44="",$E44=""),"",IF($G44&lt;$E44,"🔴 PEDIR",IF($G44&lt;$E44*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I44" s="9">
+        <f>IF(OR($G44="",$E44="",$F44=""),"",IF($G44&lt;$E44*1.5,MAX(0,$F44-$G44),0))</f>
+        <v/>
+      </c>
+      <c r="J44" s="15" t="n"/>
+      <c r="K44" s="17">
+        <f>IFERROR(IF(OR($G44="",$J44=""),"",$G44*$J44),"")</f>
+        <v/>
+      </c>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="14" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A47:H47"/>
   </mergeCells>
+  <conditionalFormatting sqref="H5:H44">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="PEDIR">
+      <formula>NOT(ISERROR(SEARCH("PEDIR",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="BAJO">
+      <formula>NOT(ISERROR(SEARCH("BAJO",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" stopIfTrue="1" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",H5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Categoría no válida" error="Elige un valor de la lista. Es la taxonomía única del kit: si cada plantilla usa palabras distintas, los SUMIF de los análisis no suman nada." promptTitle="kitinv-v2 · Categoría no válida" prompt="Las 10 categorías del kit. Son las mismas en las 9 plantillas: los análisis del 05 y del 07 agregan por este texto." type="list" errorStyle="stop">
+      <formula1>"Cárnicos,Pescados,Lácteos,Verduras/Frutas,Secos/Granos,Congelados,Bebidas Alcohólicas,Bebidas No Alcohólicas,Limpieza,Otros"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unidad no válida" error="Elige un valor de la lista. Es la taxonomía única del kit: si cada plantilla usa palabras distintas, los SUMIF de los análisis no suman nada." promptTitle="kitinv-v2 · Unidad no válida" prompt="Unidad REAL de compra: la cerveza de grifo va en barril, los huevos en docena y el vino en ud (botella de 75 cl)." type="list" errorStyle="stop">
+      <formula1>"kg,L,ud,docena,caja,bandeja,barril,saco,rollo,paquete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1551,7 +2357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1563,9 +2369,10 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1582,7 +2389,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Datos de ejemplo; precios orientativos SIN IVA, edítalos con los tuyos. Categoría y Unidad tienen desplegable.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1631,15 +2444,20 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
+          <t>Precio/ud (€)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
           <t>Valor (€)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -1649,587 +2467,1087 @@
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Café en grano</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8" t="n">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr"/>
       <c r="H5" s="8">
-        <f>IF(G5="","",IF(G5&lt;E5,"🔴 PEDIR",IF(G5&lt;E5*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G5="",$E5=""),"",IF($G5&lt;$E5,"🔴 PEDIR",IF($G5&lt;$E5*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>IF(G5="","",IF(G5&lt;E5,F5-G5,0))</f>
-        <v/>
-      </c>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
+        <f>IF(OR($G5="",$E5="",$F5=""),"",IF($G5&lt;$E5*1.5,MAX(0,$F5-$G5),0))</f>
+        <v/>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K5" s="16">
+        <f>IFERROR(IF(OR($G5="",$J5=""),"",$G5*$J5),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Leche entera</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Lácteos</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+      <c r="E6" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr"/>
       <c r="H6" s="9">
-        <f>IF(G6="","",IF(G6&lt;E6,"🔴 PEDIR",IF(G6&lt;E6*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G6="",$E6=""),"",IF($G6&lt;$E6,"🔴 PEDIR",IF($G6&lt;$E6*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>IF(G6="","",IF(G6&lt;E6,F6-G6,0))</f>
-        <v/>
-      </c>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
+        <f>IF(OR($G6="",$E6="",$F6=""),"",IF($G6&lt;$E6*1.5,MAX(0,$F6-$G6),0))</f>
+        <v/>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K6" s="17">
+        <f>IFERROR(IF(OR($G6="",$J6=""),"",$G6*$J6),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Leche avena</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Verduras</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Bebida de avena</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas No Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr"/>
       <c r="H7" s="8">
-        <f>IF(G7="","",IF(G7&lt;E7,"🔴 PEDIR",IF(G7&lt;E7*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G7="",$E7=""),"",IF($G7&lt;$E7,"🔴 PEDIR",IF($G7&lt;$E7*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IF(G7="","",IF(G7&lt;E7,F7-G7,0))</f>
-        <v/>
-      </c>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
+        <f>IF(OR($G7="",$E7="",$F7=""),"",IF($G7&lt;$E7*1.5,MAX(0,$F7-$G7),0))</f>
+        <v/>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K7" s="16">
+        <f>IFERROR(IF(OR($G7="",$J7=""),"",$G7*$J7),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Zumo naranja</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Frutas</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Zumo de naranja</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas No Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr"/>
       <c r="H8" s="9">
-        <f>IF(G8="","",IF(G8&lt;E8,"🔴 PEDIR",IF(G8&lt;E8*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G8="",$E8=""),"",IF($G8&lt;$E8,"🔴 PEDIR",IF($G8&lt;$E8*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IF(G8="","",IF(G8&lt;E8,F8-G8,0))</f>
-        <v/>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
+        <f>IF(OR($G8="",$E8="",$F8=""),"",IF($G8&lt;$E8*1.5,MAX(0,$F8-$G8),0))</f>
+        <v/>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K8" s="17">
+        <f>IFERROR(IF(OR($G8="",$J8=""),"",$G8*$J8),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Secos/Granos</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Refresco de cola</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas No Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr"/>
       <c r="H9" s="8">
-        <f>IF(G9="","",IF(G9&lt;E9,"🔴 PEDIR",IF(G9&lt;E9*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G9="",$E9=""),"",IF($G9&lt;$E9,"🔴 PEDIR",IF($G9&lt;$E9*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>IF(G9="","",IF(G9&lt;E9,F9-G9,0))</f>
-        <v/>
-      </c>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
+        <f>IF(OR($G9="",$E9="",$F9=""),"",IF($G9&lt;$E9*1.5,MAX(0,$F9-$G9),0))</f>
+        <v/>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K9" s="16">
+        <f>IFERROR(IF(OR($G9="",$J9=""),"",$G9*$J9),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Cerveza grifo (barril)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Congelados</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Cerveza de grifo (barril 30 L)</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>barril</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="14" t="inlineStr"/>
       <c r="H10" s="9">
-        <f>IF(G10="","",IF(G10&lt;E10,"🔴 PEDIR",IF(G10&lt;E10*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G10="",$E10=""),"",IF($G10&lt;$E10,"🔴 PEDIR",IF($G10&lt;$E10*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IF(G10="","",IF(G10&lt;E10,F10-G10,0))</f>
-        <v/>
-      </c>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
+        <f>IF(OR($G10="",$E10="",$F10=""),"",IF($G10&lt;$E10*1.5,MAX(0,$F10-$G10),0))</f>
+        <v/>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K10" s="17">
+        <f>IFERROR(IF(OR($G10="",$J10=""),"",$G10*$J10),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Agua mineral</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas No Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="E11" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr"/>
       <c r="H11" s="8">
-        <f>IF(G11="","",IF(G11&lt;E11,"🔴 PEDIR",IF(G11&lt;E11*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G11="",$E11=""),"",IF($G11&lt;$E11,"🔴 PEDIR",IF($G11&lt;$E11*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I11" s="8">
-        <f>IF(G11="","",IF(G11&lt;E11,F11-G11,0))</f>
-        <v/>
-      </c>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
+        <f>IF(OR($G11="",$E11="",$F11=""),"",IF($G11&lt;$E11*1.5,MAX(0,$F11-$G11),0))</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K11" s="16">
+        <f>IFERROR(IF(OR($G11="",$J11=""),"",$G11*$J11),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Tónica</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas No Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr"/>
       <c r="H12" s="9">
-        <f>IF(G12="","",IF(G12&lt;E12,"🔴 PEDIR",IF(G12&lt;E12*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G12="",$E12=""),"",IF($G12&lt;$E12,"🔴 PEDIR",IF($G12&lt;$E12*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IF(G12="","",IF(G12&lt;E12,F12-G12,0))</f>
-        <v/>
-      </c>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
+        <f>IF(OR($G12="",$E12="",$F12=""),"",IF($G12&lt;$E12*1.5,MAX(0,$F12-$G12),0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K12" s="17">
+        <f>IFERROR(IF(OR($G12="",$J12=""),"",$G12*$J12),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Vino tinto (copa)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Varios</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Vino tinto (botella 75 cl)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr"/>
       <c r="H13" s="8">
-        <f>IF(G13="","",IF(G13&lt;E13,"🔴 PEDIR",IF(G13&lt;E13*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G13="",$E13=""),"",IF($G13&lt;$E13,"🔴 PEDIR",IF($G13&lt;$E13*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I13" s="8">
-        <f>IF(G13="","",IF(G13&lt;E13,F13-G13,0))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
+        <f>IF(OR($G13="",$E13="",$F13=""),"",IF($G13&lt;$E13*1.5,MAX(0,$F13-$G13),0))</f>
+        <v/>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K13" s="16">
+        <f>IFERROR(IF(OR($G13="",$J13=""),"",$G13*$J13),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Vino blanco (copa)</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cárnicos</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Vino blanco (botella 75 cl)</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Bebidas Alcohólicas</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr"/>
+      <c r="E14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr"/>
       <c r="H14" s="9">
-        <f>IF(G14="","",IF(G14&lt;E14,"🔴 PEDIR",IF(G14&lt;E14*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G14="",$E14=""),"",IF($G14&lt;$E14,"🔴 PEDIR",IF($G14&lt;$E14*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I14" s="9">
-        <f>IF(G14="","",IF(G14&lt;E14,F14-G14,0))</f>
-        <v/>
-      </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
+        <f>IF(OR($G14="",$E14="",$F14=""),"",IF($G14&lt;$E14*1.5,MAX(0,$F14-$G14),0))</f>
+        <v/>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K14" s="17">
+        <f>IFERROR(IF(OR($G14="",$J14=""),"",$G14*$J14),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Hielo</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Hielo en cubitos</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Congelados</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>saco</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="8">
-        <f>IF(G15="","",IF(G15&lt;E15,"🔴 PEDIR",IF(G15&lt;E15*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G15="",$E15=""),"",IF($G15&lt;$E15,"🔴 PEDIR",IF($G15&lt;$E15*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IF(G15="","",IF(G15&lt;E15,F15-G15,0))</f>
-        <v/>
-      </c>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
+        <f>IF(OR($G15="",$E15="",$F15=""),"",IF($G15&lt;$E15*1.5,MAX(0,$F15-$G15),0))</f>
+        <v/>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K15" s="16">
+        <f>IFERROR(IF(OR($G15="",$J15=""),"",$G15*$J15),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Azúcar</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Lácteos</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Azúcar blanquilla</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr"/>
+      <c r="E16" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr"/>
       <c r="H16" s="9">
-        <f>IF(G16="","",IF(G16&lt;E16,"🔴 PEDIR",IF(G16&lt;E16*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G16="",$E16=""),"",IF($G16&lt;$E16,"🔴 PEDIR",IF($G16&lt;$E16*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I16" s="9">
-        <f>IF(G16="","",IF(G16&lt;E16,F16-G16,0))</f>
-        <v/>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
+        <f>IF(OR($G16="",$E16="",$F16=""),"",IF($G16&lt;$E16*1.5,MAX(0,$F16-$G16),0))</f>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K16" s="17">
+        <f>IFERROR(IF(OR($G16="",$J16=""),"",$G16*$J16),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Servilletas</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Verduras</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Servilletas de papel (barra)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>caja</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="8">
-        <f>IF(G17="","",IF(G17&lt;E17,"🔴 PEDIR",IF(G17&lt;E17*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G17="",$E17=""),"",IF($G17&lt;$E17,"🔴 PEDIR",IF($G17&lt;$E17*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I17" s="8">
-        <f>IF(G17="","",IF(G17&lt;E17,F17-G17,0))</f>
-        <v/>
-      </c>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
+        <f>IF(OR($G17="",$E17="",$F17=""),"",IF($G17&lt;$E17*1.5,MAX(0,$F17-$G17),0))</f>
+        <v/>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K17" s="16">
+        <f>IFERROR(IF(OR($G17="",$J17=""),"",$G17*$J17),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Pajitas papel</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Frutas</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr"/>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Pajitas de papel</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>caja</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr"/>
       <c r="H18" s="9">
-        <f>IF(G18="","",IF(G18&lt;E18,"🔴 PEDIR",IF(G18&lt;E18*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G18="",$E18=""),"",IF($G18&lt;$E18,"🔴 PEDIR",IF($G18&lt;$E18*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I18" s="9">
-        <f>IF(G18="","",IF(G18&lt;E18,F18-G18,0))</f>
-        <v/>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
+        <f>IF(OR($G18="",$E18="",$F18=""),"",IF($G18&lt;$E18*1.5,MAX(0,$F18-$G18),0))</f>
+        <v/>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K18" s="17">
+        <f>IFERROR(IF(OR($G18="",$J18=""),"",$G18*$J18),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Vasos desechables</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Secos/Granos</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>paquete</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr"/>
       <c r="H19" s="8">
-        <f>IF(G19="","",IF(G19&lt;E19,"🔴 PEDIR",IF(G19&lt;E19*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G19="",$E19=""),"",IF($G19&lt;$E19,"🔴 PEDIR",IF($G19&lt;$E19*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I19" s="8">
-        <f>IF(G19="","",IF(G19&lt;E19,F19-G19,0))</f>
-        <v/>
-      </c>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
+        <f>IF(OR($G19="",$E19="",$F19=""),"",IF($G19&lt;$E19*1.5,MAX(0,$F19-$G19),0))</f>
+        <v/>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" s="16">
+        <f>IFERROR(IF(OR($G19="",$J19=""),"",$G19*$J19),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="9">
+        <f>IF(OR($G20="",$E20=""),"",IF($G20&lt;$E20,"🔴 PEDIR",IF($G20&lt;$E20*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>IF(OR($G20="",$E20="",$F20=""),"",IF($G20&lt;$E20*1.5,MAX(0,$F20-$G20),0))</f>
+        <v/>
+      </c>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="17">
+        <f>IFERROR(IF(OR($G20="",$J20=""),"",$G20*$J20),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="8">
+        <f>IF(OR($G21="",$E21=""),"",IF($G21&lt;$E21,"🔴 PEDIR",IF($G21&lt;$E21*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I21" s="8">
+        <f>IF(OR($G21="",$E21="",$F21=""),"",IF($G21&lt;$E21*1.5,MAX(0,$F21-$G21),0))</f>
+        <v/>
+      </c>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="16">
+        <f>IFERROR(IF(OR($G21="",$J21=""),"",$G21*$J21),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="9">
+        <f>IF(OR($G22="",$E22=""),"",IF($G22&lt;$E22,"🔴 PEDIR",IF($G22&lt;$E22*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>IF(OR($G22="",$E22="",$F22=""),"",IF($G22&lt;$E22*1.5,MAX(0,$F22-$G22),0))</f>
+        <v/>
+      </c>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="17">
+        <f>IFERROR(IF(OR($G22="",$J22=""),"",$G22*$J22),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="8">
+        <f>IF(OR($G23="",$E23=""),"",IF($G23&lt;$E23,"🔴 PEDIR",IF($G23&lt;$E23*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I23" s="8">
+        <f>IF(OR($G23="",$E23="",$F23=""),"",IF($G23&lt;$E23*1.5,MAX(0,$F23-$G23),0))</f>
+        <v/>
+      </c>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="16">
+        <f>IFERROR(IF(OR($G23="",$J23=""),"",$G23*$J23),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="9">
+        <f>IF(OR($G24="",$E24=""),"",IF($G24&lt;$E24,"🔴 PEDIR",IF($G24&lt;$E24*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I24" s="9">
+        <f>IF(OR($G24="",$E24="",$F24=""),"",IF($G24&lt;$E24*1.5,MAX(0,$F24-$G24),0))</f>
+        <v/>
+      </c>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="17">
+        <f>IFERROR(IF(OR($G24="",$J24=""),"",$G24*$J24),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="8">
+        <f>IF(OR($G25="",$E25=""),"",IF($G25&lt;$E25,"🔴 PEDIR",IF($G25&lt;$E25*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I25" s="8">
+        <f>IF(OR($G25="",$E25="",$F25=""),"",IF($G25&lt;$E25*1.5,MAX(0,$F25-$G25),0))</f>
+        <v/>
+      </c>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="16">
+        <f>IFERROR(IF(OR($G25="",$J25=""),"",$G25*$J25),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="9">
+        <f>IF(OR($G26="",$E26=""),"",IF($G26&lt;$E26,"🔴 PEDIR",IF($G26&lt;$E26*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>IF(OR($G26="",$E26="",$F26=""),"",IF($G26&lt;$E26*1.5,MAX(0,$F26-$G26),0))</f>
+        <v/>
+      </c>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="17">
+        <f>IFERROR(IF(OR($G26="",$J26=""),"",$G26*$J26),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="8">
+        <f>IF(OR($G27="",$E27=""),"",IF($G27&lt;$E27,"🔴 PEDIR",IF($G27&lt;$E27*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I27" s="8">
+        <f>IF(OR($G27="",$E27="",$F27=""),"",IF($G27&lt;$E27*1.5,MAX(0,$F27-$G27),0))</f>
+        <v/>
+      </c>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="16">
+        <f>IFERROR(IF(OR($G27="",$J27=""),"",$G27*$J27),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="9">
+        <f>IF(OR($G28="",$E28=""),"",IF($G28&lt;$E28,"🔴 PEDIR",IF($G28&lt;$E28*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>IF(OR($G28="",$E28="",$F28=""),"",IF($G28&lt;$E28*1.5,MAX(0,$F28-$G28),0))</f>
+        <v/>
+      </c>
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="17">
+        <f>IFERROR(IF(OR($G28="",$J28=""),"",$G28*$J28),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="8">
+        <f>IF(OR($G29="",$E29=""),"",IF($G29&lt;$E29,"🔴 PEDIR",IF($G29&lt;$E29*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I29" s="8">
+        <f>IF(OR($G29="",$E29="",$F29=""),"",IF($G29&lt;$E29*1.5,MAX(0,$F29-$G29),0))</f>
+        <v/>
+      </c>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="16">
+        <f>IFERROR(IF(OR($G29="",$J29=""),"",$G29*$J29),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="9">
+        <f>IF(OR($G30="",$E30=""),"",IF($G30&lt;$E30,"🔴 PEDIR",IF($G30&lt;$E30*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>IF(OR($G30="",$E30="",$F30=""),"",IF($G30&lt;$E30*1.5,MAX(0,$F30-$G30),0))</f>
+        <v/>
+      </c>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="17">
+        <f>IFERROR(IF(OR($G30="",$J30=""),"",$G30*$J30),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="8">
+        <f>IF(OR($G31="",$E31=""),"",IF($G31&lt;$E31,"🔴 PEDIR",IF($G31&lt;$E31*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I31" s="8">
+        <f>IF(OR($G31="",$E31="",$F31=""),"",IF($G31&lt;$E31*1.5,MAX(0,$F31-$G31),0))</f>
+        <v/>
+      </c>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="16">
+        <f>IFERROR(IF(OR($G31="",$J31=""),"",$G31*$J31),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="9">
+        <f>IF(OR($G32="",$E32=""),"",IF($G32&lt;$E32,"🔴 PEDIR",IF($G32&lt;$E32*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I32" s="9">
+        <f>IF(OR($G32="",$E32="",$F32=""),"",IF($G32&lt;$E32*1.5,MAX(0,$F32-$G32),0))</f>
+        <v/>
+      </c>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="17">
+        <f>IFERROR(IF(OR($G32="",$J32=""),"",$G32*$J32),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="8">
+        <f>IF(OR($G33="",$E33=""),"",IF($G33&lt;$E33,"🔴 PEDIR",IF($G33&lt;$E33*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>IF(OR($G33="",$E33="",$F33=""),"",IF($G33&lt;$E33*1.5,MAX(0,$F33-$G33),0))</f>
+        <v/>
+      </c>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="16">
+        <f>IFERROR(IF(OR($G33="",$J33=""),"",$G33*$J33),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="9">
+        <f>IF(OR($G34="",$E34=""),"",IF($G34&lt;$E34,"🔴 PEDIR",IF($G34&lt;$E34*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I34" s="9">
+        <f>IF(OR($G34="",$E34="",$F34=""),"",IF($G34&lt;$E34*1.5,MAX(0,$F34-$G34),0))</f>
+        <v/>
+      </c>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="17">
+        <f>IFERROR(IF(OR($G34="",$J34=""),"",$G34*$J34),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <conditionalFormatting sqref="H5:H34">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="PEDIR">
+      <formula>NOT(ISERROR(SEARCH("PEDIR",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="BAJO">
+      <formula>NOT(ISERROR(SEARCH("BAJO",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" stopIfTrue="1" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",H5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Categoría no válida" error="Elige un valor de la lista. Es la taxonomía única del kit: si cada plantilla usa palabras distintas, los SUMIF de los análisis no suman nada." promptTitle="kitinv-v2 · Categoría no válida" prompt="Las 10 categorías del kit. Son las mismas en las 9 plantillas: los análisis del 05 y del 07 agregan por este texto." type="list" errorStyle="stop">
+      <formula1>"Cárnicos,Pescados,Lácteos,Verduras/Frutas,Secos/Granos,Congelados,Bebidas Alcohólicas,Bebidas No Alcohólicas,Limpieza,Otros"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unidad no válida" error="Elige un valor de la lista. Es la taxonomía única del kit: si cada plantilla usa palabras distintas, los SUMIF de los análisis no suman nada." promptTitle="kitinv-v2 · Unidad no válida" prompt="Unidad REAL de compra: la cerveza de grifo va en barril, los huevos en docena y el vino en ud (botella de 75 cl)." type="list" errorStyle="stop">
+      <formula1>"kg,L,ud,docena,caja,bandeja,barril,saco,rollo,paquete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2250,7 +3568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2262,9 +3580,10 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2281,7 +3600,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Datos de ejemplo; precios orientativos SIN IVA, edítalos con los tuyos. Categoría y Unidad tienen desplegable.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -2330,15 +3655,20 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
+          <t>Precio/ud (€)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
           <t>Valor (€)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -2348,587 +3678,1087 @@
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Papel cocina</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Papel de cocina</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>rollo</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr"/>
       <c r="H5" s="8">
-        <f>IF(G5="","",IF(G5&lt;E5,"🔴 PEDIR",IF(G5&lt;E5*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G5="",$E5=""),"",IF($G5&lt;$E5,"🔴 PEDIR",IF($G5&lt;$E5*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>IF(G5="","",IF(G5&lt;E5,F5-G5,0))</f>
-        <v/>
-      </c>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
+        <f>IF(OR($G5="",$E5="",$F5=""),"",IF($G5&lt;$E5*1.5,MAX(0,$F5-$G5),0))</f>
+        <v/>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K5" s="16">
+        <f>IFERROR(IF(OR($G5="",$J5=""),"",$G5*$J5),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Film transparente</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Lácteos</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>rollo</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr"/>
       <c r="H6" s="9">
-        <f>IF(G6="","",IF(G6&lt;E6,"🔴 PEDIR",IF(G6&lt;E6*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G6="",$E6=""),"",IF($G6&lt;$E6,"🔴 PEDIR",IF($G6&lt;$E6*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>IF(G6="","",IF(G6&lt;E6,F6-G6,0))</f>
-        <v/>
-      </c>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
+        <f>IF(OR($G6="",$E6="",$F6=""),"",IF($G6&lt;$E6*1.5,MAX(0,$F6-$G6),0))</f>
+        <v/>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K6" s="17">
+        <f>IFERROR(IF(OR($G6="",$J6=""),"",$G6*$J6),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Papel aluminio</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Verduras</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Papel de aluminio</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>rollo</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr"/>
       <c r="H7" s="8">
-        <f>IF(G7="","",IF(G7&lt;E7,"🔴 PEDIR",IF(G7&lt;E7*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G7="",$E7=""),"",IF($G7&lt;$E7,"🔴 PEDIR",IF($G7&lt;$E7*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IF(G7="","",IF(G7&lt;E7,F7-G7,0))</f>
-        <v/>
-      </c>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
+        <f>IF(OR($G7="",$E7="",$F7=""),"",IF($G7&lt;$E7*1.5,MAX(0,$F7-$G7),0))</f>
+        <v/>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K7" s="16">
+        <f>IFERROR(IF(OR($G7="",$J7=""),"",$G7*$J7),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Bolsas basura</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Frutas</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Bolsas de basura</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>paquete</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G8" s="9" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
       <c r="H8" s="9">
-        <f>IF(G8="","",IF(G8&lt;E8,"🔴 PEDIR",IF(G8&lt;E8*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G8="",$E8=""),"",IF($G8&lt;$E8,"🔴 PEDIR",IF($G8&lt;$E8*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IF(G8="","",IF(G8&lt;E8,F8-G8,0))</f>
-        <v/>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
+        <f>IF(OR($G8="",$E8="",$F8=""),"",IF($G8&lt;$E8*1.5,MAX(0,$F8-$G8),0))</f>
+        <v/>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K8" s="17">
+        <f>IFERROR(IF(OR($G8="",$J8=""),"",$G8*$J8),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Guantes nitrilo</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Secos/Granos</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Guantes de nitrilo</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>caja</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr"/>
       <c r="H9" s="8">
-        <f>IF(G9="","",IF(G9&lt;E9,"🔴 PEDIR",IF(G9&lt;E9*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G9="",$E9=""),"",IF($G9&lt;$E9,"🔴 PEDIR",IF($G9&lt;$E9*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>IF(G9="","",IF(G9&lt;E9,F9-G9,0))</f>
-        <v/>
-      </c>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
+        <f>IF(OR($G9="",$E9="",$F9=""),"",IF($G9&lt;$E9*1.5,MAX(0,$F9-$G9),0))</f>
+        <v/>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K9" s="16">
+        <f>IFERROR(IF(OR($G9="",$J9=""),"",$G9*$J9),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Lavavajillas</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Congelados</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Detergente de lavavajillas</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="14" t="inlineStr"/>
       <c r="H10" s="9">
-        <f>IF(G10="","",IF(G10&lt;E10,"🔴 PEDIR",IF(G10&lt;E10*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G10="",$E10=""),"",IF($G10&lt;$E10,"🔴 PEDIR",IF($G10&lt;$E10*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IF(G10="","",IF(G10&lt;E10,F10-G10,0))</f>
-        <v/>
-      </c>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
+        <f>IF(OR($G10="",$E10="",$F10=""),"",IF($G10&lt;$E10*1.5,MAX(0,$F10-$G10),0))</f>
+        <v/>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K10" s="17">
+        <f>IFERROR(IF(OR($G10="",$J10=""),"",$G10*$J10),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Desengrasante</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Bebidas</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8" t="n">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Desengrasante de cocina</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
       <c r="H11" s="8">
-        <f>IF(G11="","",IF(G11&lt;E11,"🔴 PEDIR",IF(G11&lt;E11*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G11="",$E11=""),"",IF($G11&lt;$E11,"🔴 PEDIR",IF($G11&lt;$E11*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I11" s="8">
-        <f>IF(G11="","",IF(G11&lt;E11,F11-G11,0))</f>
-        <v/>
-      </c>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
+        <f>IF(OR($G11="",$E11="",$F11=""),"",IF($G11&lt;$E11*1.5,MAX(0,$F11-$G11),0))</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" s="16">
+        <f>IFERROR(IF(OR($G11="",$J11=""),"",$G11*$J11),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Lejía alimentaria</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="9" t="n">
+      <c r="E12" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
       <c r="H12" s="9">
-        <f>IF(G12="","",IF(G12&lt;E12,"🔴 PEDIR",IF(G12&lt;E12*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G12="",$E12=""),"",IF($G12&lt;$E12,"🔴 PEDIR",IF($G12&lt;$E12*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IF(G12="","",IF(G12&lt;E12,F12-G12,0))</f>
-        <v/>
-      </c>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
+        <f>IF(OR($G12="",$E12="",$F12=""),"",IF($G12&lt;$E12*1.5,MAX(0,$F12-$G12),0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K12" s="17">
+        <f>IFERROR(IF(OR($G12="",$J12=""),"",$G12*$J12),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Contenedores GN 1/1</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Varios</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="8" t="n">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Cubetas GN 1/1</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
       <c r="H13" s="8">
-        <f>IF(G13="","",IF(G13&lt;E13,"🔴 PEDIR",IF(G13&lt;E13*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G13="",$E13=""),"",IF($G13&lt;$E13,"🔴 PEDIR",IF($G13&lt;$E13*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I13" s="8">
-        <f>IF(G13="","",IF(G13&lt;E13,F13-G13,0))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
+        <f>IF(OR($G13="",$E13="",$F13=""),"",IF($G13&lt;$E13*1.5,MAX(0,$F13-$G13),0))</f>
+        <v/>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" s="16">
+        <f>IFERROR(IF(OR($G13="",$J13=""),"",$G13*$J13),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Etiquetas FIFO</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cárnicos</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>rollo</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr"/>
       <c r="H14" s="9">
-        <f>IF(G14="","",IF(G14&lt;E14,"🔴 PEDIR",IF(G14&lt;E14*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G14="",$E14=""),"",IF($G14&lt;$E14,"🔴 PEDIR",IF($G14&lt;$E14*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I14" s="9">
-        <f>IF(G14="","",IF(G14&lt;E14,F14-G14,0))</f>
-        <v/>
-      </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
+        <f>IF(OR($G14="",$E14="",$F14=""),"",IF($G14&lt;$E14*1.5,MAX(0,$F14-$G14),0))</f>
+        <v/>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K14" s="17">
+        <f>IFERROR(IF(OR($G14="",$J14=""),"",$G14*$J14),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Rollos de ticket</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Pescados</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>paquete</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="F15" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="8">
-        <f>IF(G15="","",IF(G15&lt;E15,"🔴 PEDIR",IF(G15&lt;E15*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G15="",$E15=""),"",IF($G15&lt;$E15,"🔴 PEDIR",IF($G15&lt;$E15*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IF(G15="","",IF(G15&lt;E15,F15-G15,0))</f>
-        <v/>
-      </c>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
+        <f>IF(OR($G15="",$E15="",$F15=""),"",IF($G15&lt;$E15*1.5,MAX(0,$F15-$G15),0))</f>
+        <v/>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" s="16">
+        <f>IFERROR(IF(OR($G15="",$J15=""),"",$G15*$J15),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Servilletas extra</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Lácteos</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Servilletas de papel (reserva de almacén)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>caja</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr"/>
       <c r="H16" s="9">
-        <f>IF(G16="","",IF(G16&lt;E16,"🔴 PEDIR",IF(G16&lt;E16*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G16="",$E16=""),"",IF($G16&lt;$E16,"🔴 PEDIR",IF($G16&lt;$E16*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I16" s="9">
-        <f>IF(G16="","",IF(G16&lt;E16,F16-G16,0))</f>
-        <v/>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
+        <f>IF(OR($G16="",$E16="",$F16=""),"",IF($G16&lt;$E16*1.5,MAX(0,$F16-$G16),0))</f>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K16" s="17">
+        <f>IFERROR(IF(OR($G16="",$J16=""),"",$G16*$J16),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Aceite girasol (5L)</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Verduras</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="8" t="n">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Aceite de girasol (garrafa 5 L)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="F17" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="8">
-        <f>IF(G17="","",IF(G17&lt;E17,"🔴 PEDIR",IF(G17&lt;E17*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G17="",$E17=""),"",IF($G17&lt;$E17,"🔴 PEDIR",IF($G17&lt;$E17*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I17" s="8">
-        <f>IF(G17="","",IF(G17&lt;E17,F17-G17,0))</f>
-        <v/>
-      </c>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
+        <f>IF(OR($G17="",$E17="",$F17=""),"",IF($G17&lt;$E17*1.5,MAX(0,$F17-$G17),0))</f>
+        <v/>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K17" s="16">
+        <f>IFERROR(IF(OR($G17="",$J17=""),"",$G17*$J17),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Vinagre</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Frutas</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Vinagre de vino</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="9" t="n">
+      <c r="E18" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="G18" s="9" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
       <c r="H18" s="9">
-        <f>IF(G18="","",IF(G18&lt;E18,"🔴 PEDIR",IF(G18&lt;E18*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G18="",$E18=""),"",IF($G18&lt;$E18,"🔴 PEDIR",IF($G18&lt;$E18*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I18" s="9">
-        <f>IF(G18="","",IF(G18&lt;E18,F18-G18,0))</f>
-        <v/>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
+        <f>IF(OR($G18="",$E18="",$F18=""),"",IF($G18&lt;$E18*1.5,MAX(0,$F18-$G18),0))</f>
+        <v/>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K18" s="17">
+        <f>IFERROR(IF(OR($G18="",$J18=""),"",$G18*$J18),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Legumbres secas</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Secos/Granos</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="E19" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr"/>
       <c r="H19" s="8">
-        <f>IF(G19="","",IF(G19&lt;E19,"🔴 PEDIR",IF(G19&lt;E19*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <f>IF(OR($G19="",$E19=""),"",IF($G19&lt;$E19,"🔴 PEDIR",IF($G19&lt;$E19*1.5,"🟡 BAJO","🟢 OK")))</f>
         <v/>
       </c>
       <c r="I19" s="8">
-        <f>IF(G19="","",IF(G19&lt;E19,F19-G19,0))</f>
-        <v/>
-      </c>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
+        <f>IF(OR($G19="",$E19="",$F19=""),"",IF($G19&lt;$E19*1.5,MAX(0,$F19-$G19),0))</f>
+        <v/>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K19" s="16">
+        <f>IFERROR(IF(OR($G19="",$J19=""),"",$G19*$J19),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="9">
+        <f>IF(OR($G20="",$E20=""),"",IF($G20&lt;$E20,"🔴 PEDIR",IF($G20&lt;$E20*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>IF(OR($G20="",$E20="",$F20=""),"",IF($G20&lt;$E20*1.5,MAX(0,$F20-$G20),0))</f>
+        <v/>
+      </c>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="17">
+        <f>IFERROR(IF(OR($G20="",$J20=""),"",$G20*$J20),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="8">
+        <f>IF(OR($G21="",$E21=""),"",IF($G21&lt;$E21,"🔴 PEDIR",IF($G21&lt;$E21*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I21" s="8">
+        <f>IF(OR($G21="",$E21="",$F21=""),"",IF($G21&lt;$E21*1.5,MAX(0,$F21-$G21),0))</f>
+        <v/>
+      </c>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="16">
+        <f>IFERROR(IF(OR($G21="",$J21=""),"",$G21*$J21),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="9">
+        <f>IF(OR($G22="",$E22=""),"",IF($G22&lt;$E22,"🔴 PEDIR",IF($G22&lt;$E22*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>IF(OR($G22="",$E22="",$F22=""),"",IF($G22&lt;$E22*1.5,MAX(0,$F22-$G22),0))</f>
+        <v/>
+      </c>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="17">
+        <f>IFERROR(IF(OR($G22="",$J22=""),"",$G22*$J22),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="8">
+        <f>IF(OR($G23="",$E23=""),"",IF($G23&lt;$E23,"🔴 PEDIR",IF($G23&lt;$E23*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I23" s="8">
+        <f>IF(OR($G23="",$E23="",$F23=""),"",IF($G23&lt;$E23*1.5,MAX(0,$F23-$G23),0))</f>
+        <v/>
+      </c>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="16">
+        <f>IFERROR(IF(OR($G23="",$J23=""),"",$G23*$J23),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="9">
+        <f>IF(OR($G24="",$E24=""),"",IF($G24&lt;$E24,"🔴 PEDIR",IF($G24&lt;$E24*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I24" s="9">
+        <f>IF(OR($G24="",$E24="",$F24=""),"",IF($G24&lt;$E24*1.5,MAX(0,$F24-$G24),0))</f>
+        <v/>
+      </c>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="17">
+        <f>IFERROR(IF(OR($G24="",$J24=""),"",$G24*$J24),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="8">
+        <f>IF(OR($G25="",$E25=""),"",IF($G25&lt;$E25,"🔴 PEDIR",IF($G25&lt;$E25*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I25" s="8">
+        <f>IF(OR($G25="",$E25="",$F25=""),"",IF($G25&lt;$E25*1.5,MAX(0,$F25-$G25),0))</f>
+        <v/>
+      </c>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="16">
+        <f>IFERROR(IF(OR($G25="",$J25=""),"",$G25*$J25),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="9">
+        <f>IF(OR($G26="",$E26=""),"",IF($G26&lt;$E26,"🔴 PEDIR",IF($G26&lt;$E26*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>IF(OR($G26="",$E26="",$F26=""),"",IF($G26&lt;$E26*1.5,MAX(0,$F26-$G26),0))</f>
+        <v/>
+      </c>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="17">
+        <f>IFERROR(IF(OR($G26="",$J26=""),"",$G26*$J26),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="8">
+        <f>IF(OR($G27="",$E27=""),"",IF($G27&lt;$E27,"🔴 PEDIR",IF($G27&lt;$E27*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I27" s="8">
+        <f>IF(OR($G27="",$E27="",$F27=""),"",IF($G27&lt;$E27*1.5,MAX(0,$F27-$G27),0))</f>
+        <v/>
+      </c>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="16">
+        <f>IFERROR(IF(OR($G27="",$J27=""),"",$G27*$J27),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="9">
+        <f>IF(OR($G28="",$E28=""),"",IF($G28&lt;$E28,"🔴 PEDIR",IF($G28&lt;$E28*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>IF(OR($G28="",$E28="",$F28=""),"",IF($G28&lt;$E28*1.5,MAX(0,$F28-$G28),0))</f>
+        <v/>
+      </c>
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="17">
+        <f>IFERROR(IF(OR($G28="",$J28=""),"",$G28*$J28),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="8">
+        <f>IF(OR($G29="",$E29=""),"",IF($G29&lt;$E29,"🔴 PEDIR",IF($G29&lt;$E29*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I29" s="8">
+        <f>IF(OR($G29="",$E29="",$F29=""),"",IF($G29&lt;$E29*1.5,MAX(0,$F29-$G29),0))</f>
+        <v/>
+      </c>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="16">
+        <f>IFERROR(IF(OR($G29="",$J29=""),"",$G29*$J29),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="9">
+        <f>IF(OR($G30="",$E30=""),"",IF($G30&lt;$E30,"🔴 PEDIR",IF($G30&lt;$E30*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>IF(OR($G30="",$E30="",$F30=""),"",IF($G30&lt;$E30*1.5,MAX(0,$F30-$G30),0))</f>
+        <v/>
+      </c>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="17">
+        <f>IFERROR(IF(OR($G30="",$J30=""),"",$G30*$J30),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="8">
+        <f>IF(OR($G31="",$E31=""),"",IF($G31&lt;$E31,"🔴 PEDIR",IF($G31&lt;$E31*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I31" s="8">
+        <f>IF(OR($G31="",$E31="",$F31=""),"",IF($G31&lt;$E31*1.5,MAX(0,$F31-$G31),0))</f>
+        <v/>
+      </c>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="16">
+        <f>IFERROR(IF(OR($G31="",$J31=""),"",$G31*$J31),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="9">
+        <f>IF(OR($G32="",$E32=""),"",IF($G32&lt;$E32,"🔴 PEDIR",IF($G32&lt;$E32*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I32" s="9">
+        <f>IF(OR($G32="",$E32="",$F32=""),"",IF($G32&lt;$E32*1.5,MAX(0,$F32-$G32),0))</f>
+        <v/>
+      </c>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="17">
+        <f>IFERROR(IF(OR($G32="",$J32=""),"",$G32*$J32),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="8">
+        <f>IF(OR($G33="",$E33=""),"",IF($G33&lt;$E33,"🔴 PEDIR",IF($G33&lt;$E33*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>IF(OR($G33="",$E33="",$F33=""),"",IF($G33&lt;$E33*1.5,MAX(0,$F33-$G33),0))</f>
+        <v/>
+      </c>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="16">
+        <f>IFERROR(IF(OR($G33="",$J33=""),"",$G33*$J33),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="9">
+        <f>IF(OR($G34="",$E34=""),"",IF($G34&lt;$E34,"🔴 PEDIR",IF($G34&lt;$E34*1.5,"🟡 BAJO","🟢 OK")))</f>
+        <v/>
+      </c>
+      <c r="I34" s="9">
+        <f>IF(OR($G34="",$E34="",$F34=""),"",IF($G34&lt;$E34*1.5,MAX(0,$F34-$G34),0))</f>
+        <v/>
+      </c>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="17">
+        <f>IFERROR(IF(OR($G34="",$J34=""),"",$G34*$J34),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <conditionalFormatting sqref="H5:H34">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="PEDIR">
+      <formula>NOT(ISERROR(SEARCH("PEDIR",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="BAJO">
+      <formula>NOT(ISERROR(SEARCH("BAJO",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" stopIfTrue="1" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",H5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Categoría no válida" error="Elige un valor de la lista. Es la taxonomía única del kit: si cada plantilla usa palabras distintas, los SUMIF de los análisis no suman nada." promptTitle="kitinv-v2 · Categoría no válida" prompt="Las 10 categorías del kit. Son las mismas en las 9 plantillas: los análisis del 05 y del 07 agregan por este texto." type="list" errorStyle="stop">
+      <formula1>"Cárnicos,Pescados,Lácteos,Verduras/Frutas,Secos/Granos,Congelados,Bebidas Alcohólicas,Bebidas No Alcohólicas,Limpieza,Otros"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unidad no válida" error="Elige un valor de la lista. Es la taxonomía única del kit: si cada plantilla usa palabras distintas, los SUMIF de los análisis no suman nada." promptTitle="kitinv-v2 · Unidad no válida" prompt="Unidad REAL de compra: la cerveza de grifo va en barril, los huevos en docena y el vino en ud (botella de 75 cl)." type="list" errorStyle="stop">
+      <formula1>"kg,L,ud,docena,caja,bandeja,barril,saco,rollo,paquete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2949,13 +4779,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2965,7 +4795,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Todo sale solo de Cocina, Barra y Almacén: no se escribe nada aquí.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2988,8 +4824,291 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="B4" s="18">
+        <f>COUNTIF('Cocina'!$H$5:$H$44,"*BAJO*")</f>
+        <v>0.0</v>
+      </c>
+      <c r="C4" s="18">
+        <f>COUNTIF('Cocina'!$H$5:$H$44,"*PEDIR*")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="19">
+        <f>SUM('Cocina'!$K$5:$K$44)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="B5" s="18">
+        <f>COUNTIF('Barra'!$H$5:$H$34,"*BAJO*")</f>
+        <v>0.0</v>
+      </c>
+      <c r="C5" s="18">
+        <f>COUNTIF('Barra'!$H$5:$H$34,"*PEDIR*")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="19">
+        <f>SUM('Barra'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Almacén</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>COUNTIF('Almacén'!$H$5:$H$34,"*BAJO*")</f>
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="18">
+        <f>COUNTIF('Almacén'!$H$5:$H$34,"*PEDIR*")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="19">
+        <f>SUM('Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="21">
+        <f>SUM($B$4:$B$6)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C7" s="21">
+        <f>SUM($C$4:$C$6)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="22">
+        <f>SUM($D$4:$D$6)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>VALOR DEL STOCK POR CATEGORÍA</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Valor (€)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>% del Total</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cárnicos</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A10,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A10,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A10,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="23">
+        <f>IFERROR($B10/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pescados</t>
+        </is>
+      </c>
+      <c r="B11" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A11,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A11,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A11,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="23">
+        <f>IFERROR($B11/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="19" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="B12" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A12,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A12,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A12,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C12" s="23">
+        <f>IFERROR($B12/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="19" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Verduras/Frutas</t>
+        </is>
+      </c>
+      <c r="B13" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A13,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A13,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A13,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="23">
+        <f>IFERROR($B13/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Secos/Granos</t>
+        </is>
+      </c>
+      <c r="B14" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A14,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A14,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A14,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="23">
+        <f>IFERROR($B14/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Congelados</t>
+        </is>
+      </c>
+      <c r="B15" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A15,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A15,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A15,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="23">
+        <f>IFERROR($B15/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bebidas Alcohólicas</t>
+        </is>
+      </c>
+      <c r="B16" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A16,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A16,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A16,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="23">
+        <f>IFERROR($B16/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bebidas No Alcohólicas</t>
+        </is>
+      </c>
+      <c r="B17" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A17,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A17,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A17,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C17" s="23">
+        <f>IFERROR($B17/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="B18" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A18,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A18,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A18,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C18" s="23">
+        <f>IFERROR($B18/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="B19" s="19">
+        <f>SUMIF('Cocina'!$C$5:$C$44,$A19,'Cocina'!$K$5:$K$44)+SUMIF('Barra'!$C$5:$C$34,$A19,'Barra'!$K$5:$K$34)+SUMIF('Almacén'!$C$5:$C$34,$A19,'Almacén'!$K$5:$K$34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C19" s="23">
+        <f>IFERROR($B19/$B$20,"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="19" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL DEL STOCK</t>
+        </is>
+      </c>
+      <c r="B20" s="22">
+        <f>SUM($B$10:$B$19)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="19" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>El valor total de abajo y la suma de la columna «Valor total stock (€)» de arriba tienen que coincidir: si no, hay una categoría escrita a mano fuera del desplegable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
